--- a/quality/fixtures/no_dues_sample.xlsx
+++ b/quality/fixtures/no_dues_sample.xlsx
@@ -124,13 +124,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Z0004</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test Resident Four</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>100</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Total</t>
         </is>
       </c>
-      <c r="D8">
+      <c r="D9">
         <v>1500</v>
       </c>
-      <c r="E8">
+      <c r="E9">
         <v>200</v>
       </c>
     </row>
